--- a/backend/data/financials_by_company/0708.HK.xlsx
+++ b/backend/data/financials_by_company/0708.HK.xlsx
@@ -672,154 +672,154 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-9286655.497055</v>
+        <v>-378922805.75472</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00162</v>
+        <v>0.025898</v>
       </c>
       <c r="D2" t="n">
-        <v>-2163813000</v>
+        <v>-9767575000</v>
       </c>
       <c r="E2" t="n">
-        <v>-5734154000</v>
+        <v>-14631190000</v>
       </c>
       <c r="F2" t="n">
-        <v>-5734154000</v>
+        <v>-14631190000</v>
       </c>
       <c r="G2" t="n">
-        <v>-10873270000</v>
+        <v>-27220351000</v>
       </c>
       <c r="H2" t="n">
-        <v>1132679000</v>
+        <v>1806958000</v>
       </c>
       <c r="I2" t="n">
-        <v>1391359000</v>
+        <v>245826000</v>
       </c>
       <c r="J2" t="n">
-        <v>-7897967000</v>
+        <v>-24398765000</v>
       </c>
       <c r="K2" t="n">
-        <v>-9030646000</v>
+        <v>-26205723000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1916674000</v>
+        <v>-1788377000</v>
       </c>
       <c r="M2" t="n">
-        <v>1921272000</v>
+        <v>1810026000</v>
       </c>
       <c r="N2" t="n">
-        <v>4598000</v>
+        <v>21649000</v>
       </c>
       <c r="O2" t="n">
-        <v>-5148402655.497055</v>
+        <v>-12968083805.75472</v>
       </c>
       <c r="P2" t="n">
-        <v>-11934199000</v>
+        <v>-56274540000</v>
       </c>
       <c r="Q2" t="n">
-        <v>5019872000</v>
+        <v>10893930000</v>
       </c>
       <c r="R2" t="n">
-        <v>-8962165000</v>
+        <v>-24844989000</v>
       </c>
       <c r="S2" t="n">
-        <v>10843793000</v>
+        <v>9614331000</v>
       </c>
       <c r="T2" t="n">
-        <v>10843793000</v>
+        <v>9614331000</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.10056</v>
+        <v>-5.85319</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.10056</v>
+        <v>-5.85319</v>
       </c>
       <c r="W2" t="n">
-        <v>-11934199000</v>
+        <v>-56274540000</v>
       </c>
       <c r="X2" t="n">
-        <v>-11934199000</v>
+        <v>-56274540000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-11934199000</v>
+        <v>-56274540000</v>
       </c>
       <c r="AA2" t="n">
-        <v>60911000</v>
+        <v>69838000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-11995110000</v>
+        <v>-56344378000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1060929000</v>
+        <v>-29054189000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-10934181000</v>
+        <v>-27290189000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-17737000</v>
+        <v>-725560000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-10951918000</v>
+        <v>-28015749000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1018599000</v>
+        <v>-1282659000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-5661075000</v>
+        <v>-13248807000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-203510000</v>
+        <v>7488396000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1053485000</v>
+        <v>1695221000</v>
       </c>
       <c r="AK2" t="n">
-        <v>4811100000</v>
+        <v>11553586000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1916674000</v>
+        <v>-1788377000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1921272000</v>
+        <v>1810026000</v>
       </c>
       <c r="AN2" t="n">
-        <v>4598000</v>
+        <v>21649000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-3679724000</v>
+        <v>-10352041000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3628513000</v>
+        <v>10648104000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1023384000</v>
+        <v>1591250000</v>
       </c>
       <c r="AR2" t="n">
-        <v>2605129000</v>
+        <v>9080935000</v>
       </c>
       <c r="AS2" t="n">
-        <v>254907000</v>
+        <v>1285670000</v>
       </c>
       <c r="AT2" t="n">
-        <v>2350222000</v>
+        <v>7795265000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-51211000</v>
+        <v>-170840000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1391359000</v>
+        <v>245826000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1340148000</v>
+        <v>74986000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1340148000</v>
+        <v>74986000</v>
       </c>
     </row>
     <row r="3">
@@ -976,154 +976,154 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-378922805.75472</v>
+        <v>-9286655.497055</v>
       </c>
       <c r="C4" t="n">
-        <v>0.025898</v>
+        <v>0.00162</v>
       </c>
       <c r="D4" t="n">
-        <v>-9767575000</v>
+        <v>-2163813000</v>
       </c>
       <c r="E4" t="n">
-        <v>-14631190000</v>
+        <v>-5734154000</v>
       </c>
       <c r="F4" t="n">
-        <v>-14631190000</v>
+        <v>-5734154000</v>
       </c>
       <c r="G4" t="n">
-        <v>-27220351000</v>
+        <v>-10873270000</v>
       </c>
       <c r="H4" t="n">
-        <v>1806958000</v>
+        <v>1132679000</v>
       </c>
       <c r="I4" t="n">
-        <v>245826000</v>
+        <v>1391359000</v>
       </c>
       <c r="J4" t="n">
-        <v>-24398765000</v>
+        <v>-7897967000</v>
       </c>
       <c r="K4" t="n">
-        <v>-26205723000</v>
+        <v>-9030646000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1788377000</v>
+        <v>-1916674000</v>
       </c>
       <c r="M4" t="n">
-        <v>1810026000</v>
+        <v>1921272000</v>
       </c>
       <c r="N4" t="n">
-        <v>21649000</v>
+        <v>4598000</v>
       </c>
       <c r="O4" t="n">
-        <v>-12968083805.75472</v>
+        <v>-5148402655.497055</v>
       </c>
       <c r="P4" t="n">
-        <v>-56274540000</v>
+        <v>-11934199000</v>
       </c>
       <c r="Q4" t="n">
-        <v>10893930000</v>
+        <v>5019872000</v>
       </c>
       <c r="R4" t="n">
-        <v>-24844989000</v>
+        <v>-8962165000</v>
       </c>
       <c r="S4" t="n">
-        <v>9614331000</v>
+        <v>10843793000</v>
       </c>
       <c r="T4" t="n">
-        <v>9614331000</v>
+        <v>10843793000</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.85319</v>
+        <v>-1.10056</v>
       </c>
       <c r="V4" t="n">
-        <v>-5.85319</v>
+        <v>-1.10056</v>
       </c>
       <c r="W4" t="n">
-        <v>-56274540000</v>
+        <v>-11934199000</v>
       </c>
       <c r="X4" t="n">
-        <v>-56274540000</v>
+        <v>-11934199000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-56274540000</v>
+        <v>-11934199000</v>
       </c>
       <c r="AA4" t="n">
-        <v>69838000</v>
+        <v>60911000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-56344378000</v>
+        <v>-11995110000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-29054189000</v>
+        <v>-1060929000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-27290189000</v>
+        <v>-10934181000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-725560000</v>
+        <v>-17737000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-28015749000</v>
+        <v>-10951918000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1282659000</v>
+        <v>-1018599000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-13248807000</v>
+        <v>-5661075000</v>
       </c>
       <c r="AI4" t="n">
-        <v>7488396000</v>
+        <v>-203510000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1695221000</v>
+        <v>1053485000</v>
       </c>
       <c r="AK4" t="n">
-        <v>11553586000</v>
+        <v>4811100000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1788377000</v>
+        <v>-1916674000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1810026000</v>
+        <v>1921272000</v>
       </c>
       <c r="AN4" t="n">
-        <v>21649000</v>
+        <v>4598000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-10352041000</v>
+        <v>-3679724000</v>
       </c>
       <c r="AP4" t="n">
-        <v>10648104000</v>
+        <v>3628513000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1591250000</v>
+        <v>1023384000</v>
       </c>
       <c r="AR4" t="n">
-        <v>9080935000</v>
+        <v>2605129000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1285670000</v>
+        <v>254907000</v>
       </c>
       <c r="AT4" t="n">
-        <v>7795265000</v>
+        <v>2350222000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-170840000</v>
+        <v>-51211000</v>
       </c>
       <c r="AV4" t="n">
-        <v>245826000</v>
+        <v>1391359000</v>
       </c>
       <c r="AW4" t="n">
-        <v>74986000</v>
+        <v>1340148000</v>
       </c>
       <c r="AX4" t="n">
-        <v>74986000</v>
+        <v>1340148000</v>
       </c>
     </row>
   </sheetData>
@@ -1499,52 +1499,52 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>10843793000</v>
+        <v>9768963000</v>
       </c>
       <c r="C2" t="n">
-        <v>10843793000</v>
+        <v>9768963000</v>
       </c>
       <c r="D2" t="n">
-        <v>26355259000</v>
+        <v>38212385000</v>
       </c>
       <c r="E2" t="n">
-        <v>26815253000</v>
+        <v>41678640000</v>
       </c>
       <c r="F2" t="n">
-        <v>-40403299000</v>
+        <v>-49072818000</v>
       </c>
       <c r="G2" t="n">
-        <v>-11160266000</v>
+        <v>1373007000</v>
       </c>
       <c r="H2" t="n">
-        <v>-38077152000</v>
+        <v>-57251098000</v>
       </c>
       <c r="I2" t="n">
-        <v>-40403299000</v>
+        <v>-49072818000</v>
       </c>
       <c r="J2" t="n">
-        <v>331170000</v>
+        <v>1013732000</v>
       </c>
       <c r="K2" t="n">
-        <v>-37644349000</v>
+        <v>-39291901000</v>
       </c>
       <c r="L2" t="n">
-        <v>-25123444000</v>
+        <v>-28020842000</v>
       </c>
       <c r="M2" t="n">
-        <v>-37692551000</v>
+        <v>-39338982000</v>
       </c>
       <c r="N2" t="n">
-        <v>-48202000</v>
+        <v>-47081000</v>
       </c>
       <c r="O2" t="n">
-        <v>-37644349000</v>
+        <v>-39291901000</v>
       </c>
       <c r="P2" t="n">
-        <v>-110840530000</v>
+        <v>-71241322000</v>
       </c>
       <c r="Q2" t="n">
         <v>27873165000</v>
@@ -1556,157 +1556,159 @@
         <v>250936000</v>
       </c>
       <c r="T2" t="n">
-        <v>72543319000</v>
+        <v>182908356000</v>
       </c>
       <c r="U2" t="n">
-        <v>15124012000</v>
+        <v>15811518000</v>
       </c>
       <c r="V2" t="n">
-        <v>2601160000</v>
+        <v>2821150000</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1024395000</v>
       </c>
       <c r="X2" t="n">
-        <v>12522852000</v>
+        <v>11965973000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1947000</v>
+        <v>694914000</v>
       </c>
       <c r="Z2" t="n">
-        <v>12520905000</v>
+        <v>11271059000</v>
       </c>
       <c r="AA2" t="n">
-        <v>57419307000</v>
+        <v>167096838000</v>
       </c>
       <c r="AB2" t="n">
-        <v>14292401000</v>
+        <v>29712667000</v>
       </c>
       <c r="AC2" t="n">
-        <v>329223000</v>
+        <v>318818000</v>
       </c>
       <c r="AD2" t="n">
-        <v>13963178000</v>
+        <v>29393849000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1689825000</v>
+        <v>2197794000</v>
       </c>
       <c r="AF2" t="n">
-        <v>41395670000</v>
+        <v>69936739000</v>
       </c>
       <c r="AG2" t="n">
-        <v>31488608000</v>
+        <v>25853428000</v>
       </c>
       <c r="AH2" t="n">
-        <v>260496000</v>
+        <v>2431419000</v>
       </c>
       <c r="AI2" t="n">
-        <v>9646566000</v>
+        <v>41651892000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>34850768000</v>
+        <v>143569374000</v>
       </c>
       <c r="AK2" t="n">
-        <v>15508613000</v>
+        <v>33723634000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>107113000</v>
       </c>
       <c r="AM2" t="n">
-        <v>78000</v>
+        <v>151035000</v>
       </c>
       <c r="AN2" t="n">
-        <v>162289000</v>
+        <v>501493000</v>
       </c>
       <c r="AO2" t="n">
-        <v>162289000</v>
+        <v>501493000</v>
       </c>
       <c r="AP2" t="n">
-        <v>34298000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>34298000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>258475000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>614670000</v>
+      </c>
       <c r="AS2" t="n">
-        <v>2758950000</v>
+        <v>9780917000</v>
       </c>
       <c r="AT2" t="n">
-        <v>2758950000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>9780917000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
       <c r="AV2" t="n">
-        <v>12552998000</v>
+        <v>22309931000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-10689822000</v>
+        <v>-5468882000</v>
       </c>
       <c r="AX2" t="n">
-        <v>23242820000</v>
+        <v>27778813000</v>
       </c>
       <c r="AY2" t="n">
-        <v>17888384000</v>
+        <v>19311152000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>134492000</v>
+        <v>617213000</v>
       </c>
       <c r="BA2" t="n">
-        <v>1625293000</v>
+        <v>2025527000</v>
       </c>
       <c r="BB2" t="n">
-        <v>3642549000</v>
+        <v>5535435000</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>19342155000</v>
+        <v>109845740000</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>6593100000</v>
       </c>
       <c r="BF2" t="n">
-        <v>17900000</v>
+        <v>2808700000</v>
       </c>
       <c r="BG2" t="n">
-        <v>673771000</v>
+        <v>6978228000</v>
       </c>
       <c r="BH2" t="n">
-        <v>393611000</v>
+        <v>73556179000</v>
       </c>
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="n">
-        <v>157944000</v>
+        <v>73419937000</v>
       </c>
       <c r="BK2" t="n">
-        <v>8064000</v>
+        <v>55364000</v>
       </c>
       <c r="BL2" t="n">
-        <v>227603000</v>
+        <v>80878000</v>
       </c>
       <c r="BM2" t="n">
-        <v>18087306000</v>
+        <v>15088861000</v>
       </c>
       <c r="BN2" t="n">
-        <v>39997000</v>
+        <v>112753000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-41919000</v>
+        <v>-162878000</v>
       </c>
       <c r="BP2" t="n">
-        <v>81916000</v>
+        <v>275631000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>129570000</v>
+        <v>4707919000</v>
       </c>
       <c r="BR2" t="n">
-        <v>746000</v>
+        <v>2255396000</v>
       </c>
       <c r="BS2" t="n">
-        <v>128824000</v>
+        <v>2452523000</v>
       </c>
       <c r="BT2" t="n">
-        <v>128824000</v>
+        <v>2452523000</v>
       </c>
     </row>
     <row r="3">
@@ -1927,52 +1929,52 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>9768963000</v>
+        <v>10843793000</v>
       </c>
       <c r="C4" t="n">
-        <v>9768963000</v>
+        <v>10843793000</v>
       </c>
       <c r="D4" t="n">
-        <v>38212385000</v>
+        <v>26355259000</v>
       </c>
       <c r="E4" t="n">
-        <v>41678640000</v>
+        <v>26815253000</v>
       </c>
       <c r="F4" t="n">
-        <v>-49072818000</v>
+        <v>-40403299000</v>
       </c>
       <c r="G4" t="n">
-        <v>1373007000</v>
+        <v>-11160266000</v>
       </c>
       <c r="H4" t="n">
-        <v>-57251098000</v>
+        <v>-38077152000</v>
       </c>
       <c r="I4" t="n">
-        <v>-49072818000</v>
+        <v>-40403299000</v>
       </c>
       <c r="J4" t="n">
-        <v>1013732000</v>
+        <v>331170000</v>
       </c>
       <c r="K4" t="n">
-        <v>-39291901000</v>
+        <v>-37644349000</v>
       </c>
       <c r="L4" t="n">
-        <v>-28020842000</v>
+        <v>-25123444000</v>
       </c>
       <c r="M4" t="n">
-        <v>-39338982000</v>
+        <v>-37692551000</v>
       </c>
       <c r="N4" t="n">
-        <v>-47081000</v>
+        <v>-48202000</v>
       </c>
       <c r="O4" t="n">
-        <v>-39291901000</v>
+        <v>-37644349000</v>
       </c>
       <c r="P4" t="n">
-        <v>-71241322000</v>
+        <v>-110840530000</v>
       </c>
       <c r="Q4" t="n">
         <v>27873165000</v>
@@ -1984,159 +1986,157 @@
         <v>250936000</v>
       </c>
       <c r="T4" t="n">
-        <v>182908356000</v>
+        <v>72543319000</v>
       </c>
       <c r="U4" t="n">
-        <v>15811518000</v>
+        <v>15124012000</v>
       </c>
       <c r="V4" t="n">
-        <v>2821150000</v>
+        <v>2601160000</v>
       </c>
       <c r="W4" t="n">
-        <v>1024395000</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>11965973000</v>
+        <v>12522852000</v>
       </c>
       <c r="Y4" t="n">
-        <v>694914000</v>
+        <v>1947000</v>
       </c>
       <c r="Z4" t="n">
-        <v>11271059000</v>
+        <v>12520905000</v>
       </c>
       <c r="AA4" t="n">
-        <v>167096838000</v>
+        <v>57419307000</v>
       </c>
       <c r="AB4" t="n">
-        <v>29712667000</v>
+        <v>14292401000</v>
       </c>
       <c r="AC4" t="n">
-        <v>318818000</v>
+        <v>329223000</v>
       </c>
       <c r="AD4" t="n">
-        <v>29393849000</v>
+        <v>13963178000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2197794000</v>
+        <v>1689825000</v>
       </c>
       <c r="AF4" t="n">
-        <v>69936739000</v>
+        <v>41395670000</v>
       </c>
       <c r="AG4" t="n">
-        <v>25853428000</v>
+        <v>31488608000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2431419000</v>
+        <v>260496000</v>
       </c>
       <c r="AI4" t="n">
-        <v>41651892000</v>
+        <v>9646566000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>143569374000</v>
+        <v>34850768000</v>
       </c>
       <c r="AK4" t="n">
-        <v>33723634000</v>
+        <v>15508613000</v>
       </c>
       <c r="AL4" t="n">
-        <v>107113000</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>151035000</v>
+        <v>78000</v>
       </c>
       <c r="AN4" t="n">
-        <v>501493000</v>
+        <v>162289000</v>
       </c>
       <c r="AO4" t="n">
-        <v>501493000</v>
+        <v>162289000</v>
       </c>
       <c r="AP4" t="n">
-        <v>258475000</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="n">
-        <v>614670000</v>
-      </c>
+        <v>34298000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>34298000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>9780917000</v>
+        <v>2758950000</v>
       </c>
       <c r="AT4" t="n">
-        <v>9780917000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
+        <v>2758950000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>22309931000</v>
+        <v>12552998000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-5468882000</v>
+        <v>-10689822000</v>
       </c>
       <c r="AX4" t="n">
-        <v>27778813000</v>
+        <v>23242820000</v>
       </c>
       <c r="AY4" t="n">
-        <v>19311152000</v>
+        <v>17888384000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>617213000</v>
+        <v>134492000</v>
       </c>
       <c r="BA4" t="n">
-        <v>2025527000</v>
+        <v>1625293000</v>
       </c>
       <c r="BB4" t="n">
-        <v>5535435000</v>
+        <v>3642549000</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>109845740000</v>
+        <v>19342155000</v>
       </c>
       <c r="BE4" t="n">
-        <v>6593100000</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>2808700000</v>
+        <v>17900000</v>
       </c>
       <c r="BG4" t="n">
-        <v>6978228000</v>
+        <v>673771000</v>
       </c>
       <c r="BH4" t="n">
-        <v>73556179000</v>
+        <v>393611000</v>
       </c>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
-        <v>73419937000</v>
+        <v>157944000</v>
       </c>
       <c r="BK4" t="n">
-        <v>55364000</v>
+        <v>8064000</v>
       </c>
       <c r="BL4" t="n">
-        <v>80878000</v>
+        <v>227603000</v>
       </c>
       <c r="BM4" t="n">
-        <v>15088861000</v>
+        <v>18087306000</v>
       </c>
       <c r="BN4" t="n">
-        <v>112753000</v>
+        <v>39997000</v>
       </c>
       <c r="BO4" t="n">
-        <v>-162878000</v>
+        <v>-41919000</v>
       </c>
       <c r="BP4" t="n">
-        <v>275631000</v>
+        <v>81916000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4707919000</v>
+        <v>129570000</v>
       </c>
       <c r="BR4" t="n">
-        <v>2255396000</v>
+        <v>746000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2452523000</v>
+        <v>128824000</v>
       </c>
       <c r="BT4" t="n">
-        <v>2452523000</v>
+        <v>128824000</v>
       </c>
     </row>
   </sheetData>
@@ -2422,66 +2422,74 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-1440977000</v>
+        <v>-186512000</v>
       </c>
       <c r="C2" t="n">
-        <v>-219008000</v>
+        <v>-49097736000</v>
       </c>
       <c r="D2" t="n">
-        <v>412994000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>14883197000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24364691000</v>
+      </c>
       <c r="F2" t="n">
-        <v>-1189816000</v>
+        <v>-8687113000</v>
       </c>
       <c r="G2" t="n">
-        <v>128824000</v>
+        <v>2452523000</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>709074000</v>
+        <v>10476239000</v>
       </c>
       <c r="J2" t="n">
-        <v>347000</v>
+        <v>-11395000</v>
       </c>
       <c r="K2" t="n">
-        <v>-580597000</v>
+        <v>-8012321000</v>
       </c>
       <c r="L2" t="n">
-        <v>170050000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-10281219000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-42736000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>24364691000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>24364691000</v>
+      </c>
       <c r="P2" t="n">
-        <v>193986000</v>
+        <v>-34214539000</v>
       </c>
       <c r="Q2" t="n">
-        <v>193986000</v>
+        <v>-34214539000</v>
       </c>
       <c r="R2" t="n">
-        <v>-219008000</v>
+        <v>-49097736000</v>
       </c>
       <c r="S2" t="n">
-        <v>412994000</v>
+        <v>14883197000</v>
       </c>
       <c r="T2" t="n">
-        <v>-499486000</v>
+        <v>-6231703000</v>
       </c>
       <c r="U2" t="n">
-        <v>4598000</v>
+        <v>92311000</v>
       </c>
       <c r="V2" t="n">
-        <v>152584000</v>
+        <v>197966000</v>
       </c>
       <c r="W2" t="n">
-        <v>152584000</v>
+        <v>248966000</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-51000000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -2490,88 +2498,88 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-169410000</v>
+        <v>1289635000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1289635000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-169410000</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-51331000</v>
+        <v>84579000</v>
       </c>
       <c r="AE2" t="n">
-        <v>194000</v>
+        <v>185888000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-51525000</v>
+        <v>-101309000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-435927000</v>
+        <v>-7896194000</v>
       </c>
       <c r="AH2" t="n">
-        <v>702364000</v>
+        <v>689610000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1138291000</v>
+        <v>-8585804000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-251161000</v>
+        <v>8500601000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-117659000</v>
+        <v>74861000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-30700000</v>
+        <v>-3667840000</v>
       </c>
       <c r="AM2" t="n">
-        <v>3122057000</v>
+        <v>31434174000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-2832985000</v>
+        <v>859720000</v>
       </c>
       <c r="AO2" t="n">
-        <v>27064175000</v>
+        <v>55808771000</v>
       </c>
       <c r="AP2" t="n">
-        <v>407728000</v>
+        <v>269598000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>280156000</v>
+        <v>-13096627000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-21797017000</v>
+        <v>-12407288000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1916674000</v>
+        <v>3326760000</v>
       </c>
       <c r="AT2" t="n">
-        <v>122145000</v>
+        <v>719042000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1132679000</v>
+        <v>1806958000</v>
       </c>
       <c r="AV2" t="n">
-        <v>540349000</v>
+        <v>642353000</v>
       </c>
       <c r="AW2" t="n">
-        <v>592330000</v>
+        <v>1164605000</v>
       </c>
       <c r="AX2" t="n">
-        <v>82739000</v>
+        <v>1705813000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-373849000</v>
+        <v>-70909000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-490663000</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>287153000</v>
+        <v>290217000</v>
       </c>
       <c r="BB2" t="n">
-        <v>-11792551000</v>
+        <v>-57278984000</v>
       </c>
     </row>
     <row r="3">
@@ -2740,74 +2748,66 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-186512000</v>
+        <v>-1440977000</v>
       </c>
       <c r="C4" t="n">
-        <v>-49097736000</v>
+        <v>-219008000</v>
       </c>
       <c r="D4" t="n">
-        <v>14883197000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>24364691000</v>
-      </c>
+        <v>412994000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-8687113000</v>
+        <v>-1189816000</v>
       </c>
       <c r="G4" t="n">
-        <v>2452523000</v>
+        <v>128824000</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>10476239000</v>
+        <v>709074000</v>
       </c>
       <c r="J4" t="n">
-        <v>-11395000</v>
+        <v>347000</v>
       </c>
       <c r="K4" t="n">
-        <v>-8012321000</v>
+        <v>-580597000</v>
       </c>
       <c r="L4" t="n">
-        <v>-10281219000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-42736000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>24364691000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>24364691000</v>
-      </c>
+        <v>170050000</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-34214539000</v>
+        <v>193986000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-34214539000</v>
+        <v>193986000</v>
       </c>
       <c r="R4" t="n">
-        <v>-49097736000</v>
+        <v>-219008000</v>
       </c>
       <c r="S4" t="n">
-        <v>14883197000</v>
+        <v>412994000</v>
       </c>
       <c r="T4" t="n">
-        <v>-6231703000</v>
+        <v>-499486000</v>
       </c>
       <c r="U4" t="n">
-        <v>92311000</v>
+        <v>4598000</v>
       </c>
       <c r="V4" t="n">
-        <v>197966000</v>
+        <v>152584000</v>
       </c>
       <c r="W4" t="n">
-        <v>248966000</v>
+        <v>152584000</v>
       </c>
       <c r="X4" t="n">
-        <v>-51000000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2816,88 +2816,88 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1289635000</v>
+        <v>-169410000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1289635000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>-169410000</v>
       </c>
       <c r="AD4" t="n">
-        <v>84579000</v>
+        <v>-51331000</v>
       </c>
       <c r="AE4" t="n">
-        <v>185888000</v>
+        <v>194000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-101309000</v>
+        <v>-51525000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-7896194000</v>
+        <v>-435927000</v>
       </c>
       <c r="AH4" t="n">
-        <v>689610000</v>
+        <v>702364000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-8585804000</v>
+        <v>-1138291000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8500601000</v>
+        <v>-251161000</v>
       </c>
       <c r="AK4" t="n">
-        <v>74861000</v>
+        <v>-117659000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-3667840000</v>
+        <v>-30700000</v>
       </c>
       <c r="AM4" t="n">
-        <v>31434174000</v>
+        <v>3122057000</v>
       </c>
       <c r="AN4" t="n">
-        <v>859720000</v>
+        <v>-2832985000</v>
       </c>
       <c r="AO4" t="n">
-        <v>55808771000</v>
+        <v>27064175000</v>
       </c>
       <c r="AP4" t="n">
-        <v>269598000</v>
+        <v>407728000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-13096627000</v>
+        <v>280156000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-12407288000</v>
+        <v>-21797017000</v>
       </c>
       <c r="AS4" t="n">
-        <v>3326760000</v>
+        <v>1916674000</v>
       </c>
       <c r="AT4" t="n">
-        <v>719042000</v>
+        <v>122145000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1806958000</v>
+        <v>1132679000</v>
       </c>
       <c r="AV4" t="n">
-        <v>642353000</v>
+        <v>540349000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1164605000</v>
+        <v>592330000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1705813000</v>
+        <v>82739000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-70909000</v>
+        <v>-373849000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-490663000</v>
       </c>
       <c r="BA4" t="n">
-        <v>290217000</v>
+        <v>287153000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-57278984000</v>
+        <v>-11792551000</v>
       </c>
     </row>
   </sheetData>
@@ -3422,202 +3422,202 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Shawn  Siu', 'age': 54, 'title': 'Executive Chairman', 'yearBorn': 1971, 'fiscalYear': 2023, 'totalPay': 218889, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Darong  Pan', 'age': 52, 'title': 'Chief Financial Officer', 'yearBorn': 1973, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Hong  Choi', 'age': 67, 'title': 'Executive Director', 'yearBorn': 1958, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kar Chun  Fong', 'age': 50, 'title': 'Company Secretary', 'yearBorn': 1975, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yi  Yang', 'age': 62, 'title': 'President of Boao Evergrande International Hospital', 'yearBorn': 1963, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Gao  Jingshen', 'age': 57, 'title': 'Executive President of Evergrande New Energy Automobile Group', 'yearBorn': 1968, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Shawn  Siu', 'age': 54, 'title': 'Executive Chairman', 'yearBorn': 1971, 'fiscalYear': 2023, 'totalPay': 218771, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3748,7 +3748,7 @@
         <v>2.75</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.923</v>
+        <v>1.003</v>
       </c>
       <c r="AF2" t="n">
         <v>163321295</v>
@@ -3840,7 +3840,7 @@
         <v>10843793000</v>
       </c>
       <c r="BI2" t="n">
-        <v>-6.1867933</v>
+        <v>-6.183462</v>
       </c>
       <c r="BJ2" t="n">
         <v>1703980800</v>
@@ -3875,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="n">
         <v>0.00013</v>
@@ -3982,153 +3982,153 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CX2" t="n">
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>EVERG VEHICLE</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>finmb_40398024</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
         <v>1.1904787</v>
       </c>
-      <c r="CY2" t="n">
+      <c r="DG2" t="n">
         <v>0.17</v>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>China Evergrande New Energy Vehicle Group Limited</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1743408508</v>
+      </c>
+      <c r="DK2" t="inlineStr">
         <is>
           <t>PREPRE</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.027477887</v>
-      </c>
-      <c r="DF2" t="n">
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1202779800000</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.002000004</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>0.17 - 0.214</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>0.17 - 0.214</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.20560747</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1725029110</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1725029110</v>
+      </c>
+      <c r="DZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.027492689</v>
+      </c>
+      <c r="EG2" t="n">
         <v>15</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="EH2" t="n">
         <v>15</v>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>Evergrande Health Industry Group Limited</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>EVERG VEHICLE</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>China Evergrande New Energy Vehicle Group Limited</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>1743408508</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>finmb_40398024</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1202779800000</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0.002000004</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>0.17 - 0.214</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>0.17 - 0.214</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.044</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.20560747</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1725029110</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1725029110</v>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-2.7</v>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EK2" t="b">
+        <v>0</v>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
